--- a/public/templates/feeder-master-template.xlsx
+++ b/public/templates/feeder-master-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
   <si>
     <t>feeder_name</t>
   </si>
@@ -41,6 +41,15 @@
     <t>item_vendor_cat</t>
   </si>
   <si>
+    <t>item_name</t>
+  </si>
+  <si>
+    <t>item_make</t>
+  </si>
+  <si>
+    <t>item_category</t>
+  </si>
+  <si>
     <t>item_qty</t>
   </si>
   <si>
@@ -65,9 +74,24 @@
     <t>SKU-ACB-4000</t>
   </si>
   <si>
+    <t>Emax 2 E6.2 4000A Withdrawable ACB</t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
     <t>SKU-CT-4000</t>
   </si>
   <si>
+    <t>4000/5A CT</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
     <t>Outgoing MCCB 630A</t>
   </si>
   <si>
@@ -86,6 +110,9 @@
     <t>VC-MCCB-630</t>
   </si>
   <si>
+    <t>Tmax XT7 630A MCCB</t>
+  </si>
+  <si>
     <t>How to fill this template</t>
   </si>
   <si>
@@ -125,10 +152,22 @@
     <t>if left blank.</t>
   </si>
   <si>
-    <t>If an item_sku/item_vendor_cat isn't found in Item Master, you'll be asked to fill in the minimum</t>
-  </si>
-  <si>
-    <t>details to create it (or choose not to) before the import finishes.</t>
+    <t>If an item_sku/item_vendor_cat isn't already in Item Master, item_name (its description), item_make,</t>
+  </si>
+  <si>
+    <t>and item_category pre-fill the item-creation review step -- fill them in here to skip typing them</t>
+  </si>
+  <si>
+    <t>there. Item Master requires Description, Make, Category, and Source to create any item; ACB, MCCB,</t>
+  </si>
+  <si>
+    <t>and MCB items also require Amps, Poles, and kA -- those three aren't on this template (they're</t>
+  </si>
+  <si>
+    <t>specific to the physical item, not the feeder), so you'll fill them in on the review step when</t>
+  </si>
+  <si>
+    <t>item_category is ACB, MCCB, or MCB.</t>
   </si>
 </sst>
 </file>
@@ -520,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -529,10 +568,12 @@
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -563,100 +604,136 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>4000</v>
       </c>
       <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>630</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4">
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -668,7 +745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -676,102 +753,122 @@
   <sheetData>
     <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
